--- a/data/btc_halving_peak_dates.xlsx
+++ b/data/btc_halving_peak_dates.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-08-15</t>
         </is>
       </c>
     </row>
